--- a/SGC-CKN/Excel/b353ead4-13e6-4f3c-8d89-64e856e8c855_Đường_kính_cọc_D800_P7-74_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/b353ead4-13e6-4f3c-8d89-64e856e8c855_Đường_kính_cọc_D800_P7-74_D800_06-04-2026.xlsx
@@ -98,7 +98,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">00:51
+    <t xml:space="preserve">03:00
 05/04/2026</t>
   </si>
   <si>
@@ -125,7 +125,7 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">05:00
+    <t xml:space="preserve">06:00
 05/04/2026</t>
   </si>
   <si>
@@ -145,7 +145,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">07:50
+    <t xml:space="preserve">07:30
 05/04/2026</t>
   </si>
   <si>
@@ -159,11 +159,11 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">08:58
+    <t xml:space="preserve">08:38
 05/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">12:05
+    <t xml:space="preserve">12:03
 05/04/2026</t>
   </si>
   <si>
@@ -177,7 +177,7 @@
 05/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">17:41
+    <t xml:space="preserve">14:01
 05/04/2026</t>
   </si>
   <si>
@@ -187,11 +187,11 @@
     <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">17:02
+    <t xml:space="preserve">14:02
 05/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">19:40
+    <t xml:space="preserve">14:40
 05/04/2026</t>
   </si>
   <si>
@@ -202,11 +202,11 @@
   </si>
   <si>
     <t xml:space="preserve">07:30
-05/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">08:59
-05/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -216,11 +216,11 @@
   </si>
   <si>
     <t xml:space="preserve">09:00
-05/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:14
-05/04/2026</t>
+06/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -323,12 +323,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF164E63"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -340,6 +334,12 @@
     </font>
     <font>
       <color rgb="FF134E4A"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -385,7 +385,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -395,12 +395,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -425,11 +425,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
@@ -441,6 +436,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -571,17 +571,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -622,6 +622,12 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -642,12 +648,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1241,19 +1241,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.28</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.92</v>
       </c>
       <c r="H11" s="5">
-        <v>2.82</v>
+        <v>0.67</v>
       </c>
       <c r="I11" s="5">
-        <v>3.64</v>
+        <v>6.92</v>
       </c>
       <c r="J11" s="8">
-        <v>1.29</v>
+        <v>10.38</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1287,7 +1287,7 @@
       <c r="I12" s="9">
         <v>2.03</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="12">
         <v>1.74</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1295,37 +1295,37 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>-8.95</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>-17.15</v>
       </c>
-      <c r="H13" s="12">
-        <v>0.17</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="H13" s="13">
+        <v>1.17</v>
+      </c>
+      <c r="I13" s="13">
         <v>8.2</v>
       </c>
-      <c r="J13" s="15">
-        <v>49.2</v>
-      </c>
-      <c r="K13" s="13" t="s">
+      <c r="J13" s="8">
+        <v>7.03</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1352,13 +1352,13 @@
         <v>-21.5</v>
       </c>
       <c r="H14" s="16">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="I14" s="16">
         <v>4.35</v>
       </c>
       <c r="J14" s="8">
-        <v>2.49</v>
+        <v>5.8</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1387,13 +1387,13 @@
         <v>-26.5</v>
       </c>
       <c r="H15" s="19">
-        <v>0.78</v>
+        <v>1.12</v>
       </c>
       <c r="I15" s="19">
         <v>5</v>
       </c>
-      <c r="J15" s="15">
-        <v>6.38</v>
+      <c r="J15" s="12">
+        <v>4.48</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1419,16 +1419,16 @@
         <v>-26.5</v>
       </c>
       <c r="G16" s="22">
-        <v>-30.23</v>
+        <v>-36.23</v>
       </c>
       <c r="H16" s="22">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="I16" s="22">
-        <v>3.73</v>
-      </c>
-      <c r="J16" s="8">
-        <v>1.2</v>
+        <v>9.73</v>
+      </c>
+      <c r="J16" s="12">
+        <v>2.85</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1451,126 +1451,126 @@
         <v>51</v>
       </c>
       <c r="F17" s="25">
-        <v>-30.23</v>
+        <v>-36.23</v>
       </c>
       <c r="G17" s="25">
-        <v>-33.78</v>
+        <v>-38.23</v>
       </c>
       <c r="H17" s="25">
-        <v>4.6</v>
+        <v>0.93</v>
       </c>
       <c r="I17" s="25">
-        <v>3.55</v>
-      </c>
-      <c r="J17" s="28">
-        <v>0.77</v>
+        <v>2</v>
+      </c>
+      <c r="J17" s="12">
+        <v>2.14</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="29">
-        <v>-33.78</v>
-      </c>
-      <c r="G18" s="29">
-        <v>-39.54</v>
-      </c>
-      <c r="H18" s="29">
-        <v>2.63</v>
-      </c>
-      <c r="I18" s="29">
-        <v>5.76</v>
-      </c>
-      <c r="J18" s="8">
-        <v>2.19</v>
-      </c>
-      <c r="K18" s="30" t="s">
+      <c r="F18" s="28">
+        <v>-38.23</v>
+      </c>
+      <c r="G18" s="28">
+        <v>-39.59</v>
+      </c>
+      <c r="H18" s="28">
+        <v>0.63</v>
+      </c>
+      <c r="I18" s="28">
+        <v>1.36</v>
+      </c>
+      <c r="J18" s="12">
+        <v>2.15</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="32">
-        <v>-39.54</v>
-      </c>
-      <c r="G19" s="32">
-        <v>-45.54</v>
-      </c>
-      <c r="H19" s="32">
+      <c r="F19" s="31">
+        <v>-39.59</v>
+      </c>
+      <c r="G19" s="31">
+        <v>-43.59</v>
+      </c>
+      <c r="H19" s="31">
         <v>1.48</v>
       </c>
-      <c r="I19" s="32">
-        <v>6</v>
-      </c>
-      <c r="J19" s="8">
-        <v>4.04</v>
-      </c>
-      <c r="K19" s="33" t="s">
+      <c r="I19" s="31">
+        <v>4</v>
+      </c>
+      <c r="J19" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="K19" s="32" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="35">
-        <v>-45.54</v>
-      </c>
-      <c r="G20" s="35">
-        <v>-49.65</v>
-      </c>
-      <c r="H20" s="35">
+      <c r="F20" s="34">
+        <v>-43.59</v>
+      </c>
+      <c r="G20" s="34">
+        <v>-44.65</v>
+      </c>
+      <c r="H20" s="34">
         <v>1.23</v>
       </c>
-      <c r="I20" s="35">
-        <v>4.11</v>
-      </c>
-      <c r="J20" s="8">
-        <v>3.33</v>
-      </c>
-      <c r="K20" s="36" t="s">
+      <c r="I20" s="34">
+        <v>1.06</v>
+      </c>
+      <c r="J20" s="37">
+        <v>0.86</v>
+      </c>
+      <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1723,19 +1723,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.28</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.92</v>
       </c>
       <c r="G2" s="5">
-        <v>2.82</v>
+        <v>0.67</v>
       </c>
       <c r="H2" s="5">
-        <v>3.64</v>
+        <v>6.92</v>
       </c>
       <c r="I2" s="8">
-        <v>1.29</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1763,37 +1763,37 @@
       <c r="H3" s="9">
         <v>2.03</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="12">
         <v>1.74</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-8.95</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>-17.15</v>
       </c>
-      <c r="G4" s="12">
-        <v>0.17</v>
-      </c>
-      <c r="H4" s="12">
+      <c r="G4" s="13">
+        <v>1.17</v>
+      </c>
+      <c r="H4" s="13">
         <v>8.2</v>
       </c>
-      <c r="I4" s="15">
-        <v>49.2</v>
+      <c r="I4" s="8">
+        <v>7.03</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1816,13 +1816,13 @@
         <v>-21.5</v>
       </c>
       <c r="G5" s="16">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="16">
         <v>4.35</v>
       </c>
       <c r="I5" s="8">
-        <v>2.49</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1845,13 +1845,13 @@
         <v>-26.5</v>
       </c>
       <c r="G6" s="19">
-        <v>0.78</v>
+        <v>1.12</v>
       </c>
       <c r="H6" s="19">
         <v>5</v>
       </c>
-      <c r="I6" s="15">
-        <v>6.38</v>
+      <c r="I6" s="12">
+        <v>4.48</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1871,16 +1871,16 @@
         <v>-26.5</v>
       </c>
       <c r="F7" s="22">
-        <v>-30.23</v>
+        <v>-36.23</v>
       </c>
       <c r="G7" s="22">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="H7" s="22">
-        <v>3.73</v>
-      </c>
-      <c r="I7" s="8">
-        <v>1.2</v>
+        <v>9.73</v>
+      </c>
+      <c r="I7" s="12">
+        <v>2.85</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1897,106 +1897,106 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-30.23</v>
+        <v>-36.23</v>
       </c>
       <c r="F8" s="25">
-        <v>-33.78</v>
+        <v>-38.23</v>
       </c>
       <c r="G8" s="25">
-        <v>4.6</v>
+        <v>0.93</v>
       </c>
       <c r="H8" s="25">
-        <v>3.55</v>
-      </c>
-      <c r="I8" s="28">
-        <v>0.77</v>
+        <v>2</v>
+      </c>
+      <c r="I8" s="12">
+        <v>2.14</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
-        <v>-33.78</v>
-      </c>
-      <c r="F9" s="29">
-        <v>-39.54</v>
-      </c>
-      <c r="G9" s="29">
-        <v>2.63</v>
-      </c>
-      <c r="H9" s="29">
-        <v>5.76</v>
-      </c>
-      <c r="I9" s="8">
-        <v>2.19</v>
+      <c r="E9" s="28">
+        <v>-38.23</v>
+      </c>
+      <c r="F9" s="28">
+        <v>-39.59</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0.63</v>
+      </c>
+      <c r="H9" s="28">
+        <v>1.36</v>
+      </c>
+      <c r="I9" s="12">
+        <v>2.15</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="32">
-        <v>-39.54</v>
-      </c>
-      <c r="F10" s="32">
-        <v>-45.54</v>
-      </c>
-      <c r="G10" s="32">
+      <c r="E10" s="31">
+        <v>-39.59</v>
+      </c>
+      <c r="F10" s="31">
+        <v>-43.59</v>
+      </c>
+      <c r="G10" s="31">
         <v>1.48</v>
       </c>
-      <c r="H10" s="32">
-        <v>6</v>
-      </c>
-      <c r="I10" s="8">
-        <v>4.04</v>
+      <c r="H10" s="31">
+        <v>4</v>
+      </c>
+      <c r="I10" s="12">
+        <v>2.7</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
-        <v>-45.54</v>
-      </c>
-      <c r="F11" s="35">
-        <v>-49.65</v>
-      </c>
-      <c r="G11" s="35">
+      <c r="E11" s="34">
+        <v>-43.59</v>
+      </c>
+      <c r="F11" s="34">
+        <v>-44.65</v>
+      </c>
+      <c r="G11" s="34">
         <v>1.23</v>
       </c>
-      <c r="H11" s="35">
-        <v>4.11</v>
-      </c>
-      <c r="I11" s="8">
-        <v>3.33</v>
+      <c r="H11" s="34">
+        <v>1.06</v>
+      </c>
+      <c r="I11" s="37">
+        <v>0.86</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2013,19 +2013,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-3.28</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
-        <v>-49.65</v>
+        <v>-44.65</v>
       </c>
       <c r="G12" s="40">
-        <v>19.75</v>
+        <v>12.57</v>
       </c>
       <c r="H12" s="40">
-        <v>46.37</v>
+        <v>44.65</v>
       </c>
       <c r="I12" s="40">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
     </row>
   </sheetData>
